--- a/output/StructureDefinition-Person.xlsx
+++ b/output/StructureDefinition-Person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3798" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3798" uniqueCount="619">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025.2.0</t>
+    <t>2026.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-05</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1072,7 +1072,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>AC</t>
@@ -1082,10 +1082,6 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Person.name.prefix.value</t>
@@ -6671,7 +6667,7 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>101</v>
@@ -6737,7 +6733,7 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>20</v>
@@ -7064,7 +7060,7 @@
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>344</v>
+        <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>97</v>
@@ -7081,10 +7077,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7110,10 +7106,10 @@
         <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7137,34 +7133,34 @@
         <v>20</v>
       </c>
       <c r="W44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -7190,10 +7186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7219,10 +7215,10 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>311</v>
@@ -7275,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7290,21 +7286,21 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7330,16 +7326,16 @@
         <v>247</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>250</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7388,7 +7384,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7403,21 +7399,21 @@
         <v>252</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7440,19 +7436,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7489,7 +7485,7 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7499,7 +7495,7 @@
         <v>113</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -7511,27 +7507,27 @@
         <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AK47" t="s" s="2">
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7553,19 +7549,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7614,7 +7610,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7626,24 +7622,24 @@
         <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7749,10 +7745,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7860,10 +7856,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7889,10 +7885,10 @@
         <v>164</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>311</v>
@@ -7906,7 +7902,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -7924,57 +7920,57 @@
         <v>214</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Z51" t="s" s="2">
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI51" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8000,16 +7996,16 @@
         <v>100</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8058,7 +8054,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8073,21 +8069,21 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8113,16 +8109,16 @@
         <v>164</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8150,28 +8146,28 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z53" t="s" s="2">
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -8192,15 +8188,15 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8223,16 +8219,16 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8282,7 +8278,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8308,10 +8304,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8337,10 +8333,10 @@
         <v>247</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>250</v>
@@ -8393,7 +8389,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -8408,7 +8404,7 @@
         <v>252</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8419,13 +8415,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8447,19 +8443,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8508,7 +8504,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8520,24 +8516,24 @@
         <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AK56" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AK56" t="s" s="2">
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8643,10 +8639,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8754,10 +8750,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8783,10 +8779,10 @@
         <v>164</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>311</v>
@@ -8800,7 +8796,7 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>20</v>
@@ -8818,57 +8814,57 @@
         <v>214</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="Z59" t="s" s="2">
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
+      <c r="AG59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8894,16 +8890,16 @@
         <v>100</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8952,7 +8948,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8967,21 +8963,21 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9007,16 +9003,16 @@
         <v>164</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9044,28 +9040,28 @@
         <v>214</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="Z61" t="s" s="2">
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9086,15 +9082,15 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9117,16 +9113,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9176,7 +9172,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9202,10 +9198,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9231,10 +9227,10 @@
         <v>247</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>250</v>
@@ -9287,7 +9283,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9302,7 +9298,7 @@
         <v>252</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9313,10 +9309,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9342,16 +9338,16 @@
         <v>164</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9379,11 +9375,11 @@
         <v>214</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9400,7 +9396,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9415,21 +9411,21 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>437</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9452,19 +9448,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9513,7 +9509,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9528,21 +9524,21 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9565,19 +9561,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9626,7 +9622,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9641,21 +9637,21 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>453</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9761,10 +9757,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9872,10 +9868,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9901,16 +9897,16 @@
         <v>164</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9923,7 +9919,7 @@
         <v>20</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>20</v>
@@ -9938,28 +9934,28 @@
         <v>214</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9980,15 +9976,15 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10014,13 +10010,13 @@
         <v>164</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10034,7 +10030,7 @@
         <v>20</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>20</v>
@@ -10049,28 +10045,28 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Z70" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -10091,15 +10087,15 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10125,13 +10121,13 @@
         <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>288</v>
@@ -10147,43 +10143,43 @@
         <v>20</v>
       </c>
       <c r="T71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -10204,15 +10200,15 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10238,10 +10234,10 @@
         <v>100</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>311</v>
@@ -10258,43 +10254,43 @@
         <v>20</v>
       </c>
       <c r="T72" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10309,25 +10305,25 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10349,10 +10345,10 @@
         <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>311</v>
@@ -10369,43 +10365,43 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10420,25 +10416,25 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10460,13 +10456,13 @@
         <v>100</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10480,43 +10476,43 @@
         <v>20</v>
       </c>
       <c r="T74" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10531,25 +10527,25 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>505</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10571,10 +10567,10 @@
         <v>100</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>311</v>
@@ -10627,7 +10623,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10642,25 +10638,25 @@
         <v>97</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10682,10 +10678,10 @@
         <v>100</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>311</v>
@@ -10702,43 +10698,43 @@
         <v>20</v>
       </c>
       <c r="T76" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10753,21 +10749,21 @@
         <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10793,13 +10789,13 @@
         <v>100</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10849,7 +10845,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10864,21 +10860,21 @@
         <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>527</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10904,16 +10900,16 @@
         <v>247</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>250</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10926,43 +10922,43 @@
         <v>20</v>
       </c>
       <c r="T78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10977,21 +10973,21 @@
         <v>252</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11014,16 +11010,16 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11073,7 +11069,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -11085,24 +11081,24 @@
         <v>96</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AK79" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AK79" t="s" s="2">
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11128,16 +11124,16 @@
         <v>256</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11186,7 +11182,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -11201,7 +11197,7 @@
         <v>261</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -11212,10 +11208,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11321,10 +11317,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11432,10 +11428,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11461,13 +11457,13 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11517,16 +11513,16 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>97</v>
@@ -11543,10 +11539,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11572,13 +11568,13 @@
         <v>128</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11607,28 +11603,28 @@
         <v>144</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11654,10 +11650,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11683,13 +11679,13 @@
         <v>200</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11739,7 +11735,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11754,21 +11750,21 @@
         <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>570</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11874,10 +11870,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11985,10 +11981,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12098,10 +12094,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12211,10 +12207,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12324,10 +12320,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12435,10 +12431,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12546,10 +12542,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12657,10 +12653,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12686,13 +12682,13 @@
         <v>100</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12742,7 +12738,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12768,10 +12764,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12794,17 +12790,17 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -12853,7 +12849,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12868,10 +12864,10 @@
         <v>97</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AL95" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -12879,10 +12875,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12905,13 +12901,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12962,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12977,7 +12973,7 @@
         <v>97</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>
@@ -12988,10 +12984,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13097,10 +13093,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13208,14 +13204,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13237,10 +13233,10 @@
         <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>110</v>
@@ -13295,7 +13291,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -13321,10 +13317,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13347,16 +13343,16 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>606</v>
-      </c>
       <c r="N100" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13406,7 +13402,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>84</v>
@@ -13421,7 +13417,7 @@
         <v>261</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>20</v>
@@ -13432,10 +13428,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13541,10 +13537,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13652,10 +13648,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13681,13 +13677,13 @@
         <v>100</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13737,16 +13733,16 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>97</v>
@@ -13763,10 +13759,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13792,13 +13788,13 @@
         <v>128</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13827,28 +13823,28 @@
         <v>144</v>
       </c>
       <c r="Y104" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z104" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="Z104" t="s" s="2">
+      <c r="AA104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13874,10 +13870,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13903,13 +13899,13 @@
         <v>200</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13959,7 +13955,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -13974,21 +13970,21 @@
         <v>97</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM105" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>570</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14014,13 +14010,13 @@
         <v>100</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14070,7 +14066,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14096,10 +14092,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14125,10 +14121,10 @@
         <v>164</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>311</v>
@@ -14160,11 +14156,11 @@
         <v>214</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>618</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
       </c>
@@ -14181,7 +14177,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14196,7 +14192,7 @@
         <v>97</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>20</v>

--- a/output/StructureDefinition-Person.xlsx
+++ b/output/StructureDefinition-Person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3798" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Person(classCode="PSN" and determinerCode="INST" and quantity="1")</t>
@@ -310,318 +310,315 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Person.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Person.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Person.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Person.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Person.meta.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Person.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Person.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Person.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Person.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Person.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Person.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Person.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Person.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Person.extension:customIdatValues</t>
+  </si>
+  <si>
+    <t>customIdatValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://ths-greifswald.de/fhir/StructureDefinition/epix/CustomIdatValues}
+</t>
+  </si>
+  <si>
+    <t>Custom IDAT Values</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Person.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Person.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Person.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Person.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Person.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Person.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Person.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>Person.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Person.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Person.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Person.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Person.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>Person.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Person.extension:customIdatValues</t>
-  </si>
-  <si>
-    <t>customIdatValues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://ths-greifswald.de/fhir/StructureDefinition/epix/CustomIdatValues}
-</t>
-  </si>
-  <si>
-    <t>Custom IDAT Values</t>
-  </si>
-  <si>
     <t>Person.modifierExtension</t>
   </si>
   <si>
@@ -794,15 +791,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -830,10 +819,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -984,9 +969,6 @@
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>HumanName.prefix</t>
   </si>
   <si>
@@ -997,6 +979,12 @@
   </si>
   <si>
     <t>Person.name.prefix.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
   </si>
   <si>
     <t>Person.name.prefix.extension</t>
@@ -1036,12 +1024,6 @@
     <t>Person.name.prefix.extension.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>Person.name.prefix.extension:academic.url</t>
   </si>
   <si>
@@ -1088,6 +1070,9 @@
   </si>
   <si>
     <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
   </si>
   <si>
     <t>1048576</t>
@@ -1158,10 +1143,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>./telecom</t>
   </si>
   <si>
@@ -1207,8 +1188,8 @@
     <t>ContactPoint.system</t>
   </si>
   <si>
-    <t>ele-1
-cpt-2</t>
+    <t xml:space="preserve">cpt-2
+</t>
   </si>
   <si>
     <t>./scheme</t>
@@ -1681,13 +1662,6 @@
     <t>An image that can be displayed as a thumbnail of the person to enhance the identification of the individual.</t>
   </si>
   <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
-  </si>
-  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/desc</t>
   </si>
   <si>
@@ -1703,9 +1677,6 @@
     <t>repräsentiert hier die Domäne, zur der der MPI-Eintrag gehört.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Need to know who recognizes this person record, manages and updates it.</t>
   </si>
   <si>
@@ -1733,8 +1704,8 @@
     <t>Reference.reference</t>
   </si>
   <si>
-    <t>ele-1
-ref-1</t>
+    <t xml:space="preserve">ref-1
+</t>
   </si>
   <si>
     <t>Person.managingOrganization.type</t>
@@ -1778,9 +1749,6 @@
   </si>
   <si>
     <t>.identifier</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
   </si>
   <si>
     <t>Person.managingOrganization.identifier.id</t>
@@ -2731,13 +2699,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>20</v>
@@ -2748,10 +2716,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2774,13 +2742,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2831,7 +2799,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -2846,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>20</v>
@@ -2857,14 +2825,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2883,16 +2851,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2930,19 +2898,19 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
@@ -2951,13 +2919,13 @@
         <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>20</v>
@@ -2968,10 +2936,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2997,13 +2965,13 @@
         <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3053,7 +3021,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -3062,13 +3030,13 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>20</v>
@@ -3079,10 +3047,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3105,16 +3073,16 @@
         <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3164,7 +3132,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
@@ -3173,13 +3141,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ8" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK8" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>20</v>
@@ -3190,10 +3158,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3216,16 +3184,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3275,7 +3243,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -3284,13 +3252,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK9" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>20</v>
@@ -3301,10 +3269,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3327,16 +3295,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3386,7 +3354,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -3395,13 +3363,13 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>20</v>
@@ -3412,10 +3380,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3438,16 +3406,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3473,31 +3441,31 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -3506,27 +3474,27 @@
         <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3549,16 +3517,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3584,13 +3552,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3608,7 +3576,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -3617,27 +3585,27 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>149</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3660,16 +3628,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3719,7 +3687,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3728,13 +3696,13 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
@@ -3745,10 +3713,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3771,16 +3739,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3806,13 +3774,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3830,7 +3798,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3839,13 +3807,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3856,14 +3824,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3882,16 +3850,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3941,7 +3909,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3950,13 +3918,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3967,14 +3935,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3993,16 +3961,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4052,7 +4020,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -4067,7 +4035,7 @@
         <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -4078,14 +4046,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4104,17 +4072,15 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4151,19 +4117,17 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC17" s="2"/>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC17" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -4172,13 +4136,13 @@
         <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
@@ -4189,13 +4153,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>20</v>
@@ -4217,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4274,7 +4238,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -4283,10 +4247,10 @@
         <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4300,14 +4264,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4326,19 +4290,19 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O19" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4375,19 +4339,19 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -4396,13 +4360,13 @@
         <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
@@ -4413,10 +4377,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4439,17 +4403,17 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4498,7 +4462,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -4507,27 +4471,27 @@
         <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4550,13 +4514,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4607,7 +4571,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -4622,7 +4586,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -4633,14 +4597,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4659,16 +4623,16 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4706,19 +4670,19 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC22" t="s" s="2">
+      <c r="AF22" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4727,13 +4691,13 @@
         <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -4744,10 +4708,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4770,19 +4734,19 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4807,60 +4771,60 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y23" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Z23" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AA23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF23" t="s" s="2">
+      <c r="AG23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4883,19 +4847,19 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4920,60 +4884,60 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4996,19 +4960,19 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5021,72 +4985,72 @@
         <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="U25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5109,16 +5073,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5132,72 +5096,72 @@
         <v>20</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="U26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF26" t="s" s="2">
+      <c r="AG26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5220,17 +5184,15 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5279,36 +5241,36 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,16 +5293,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5390,7 +5352,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -5399,27 +5361,27 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="AK28" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5442,19 +5404,19 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5503,7 +5465,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -5512,27 +5474,27 @@
         <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK29" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5555,13 +5517,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5612,7 +5574,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -5627,7 +5589,7 @@
         <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
@@ -5638,14 +5600,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5664,16 +5626,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5711,19 +5673,19 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5732,13 +5694,13 @@
         <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5749,10 +5711,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5775,19 +5737,19 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5812,60 +5774,60 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5888,19 +5850,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5949,7 +5911,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5958,31 +5920,31 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK33" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6001,16 +5963,16 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6060,7 +6022,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -6069,31 +6031,31 @@
         <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK34" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6112,16 +6074,16 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6171,7 +6133,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -6180,27 +6142,27 @@
         <v>76</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6223,17 +6185,15 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6282,7 +6242,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -6291,27 +6251,27 @@
         <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK36" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6334,13 +6294,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>101</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
+        <v>312</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6391,7 +6351,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -6406,7 +6366,7 @@
         <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6417,14 +6377,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6443,17 +6403,15 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6490,19 +6448,17 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC38" s="2"/>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC38" t="s" s="2">
+      <c r="AF38" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -6511,13 +6467,13 @@
         <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6528,13 +6484,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -6556,16 +6512,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6615,7 +6571,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6624,13 +6580,13 @@
         <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -6641,10 +6597,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6667,13 +6623,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6724,7 +6680,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6739,7 +6695,7 @@
         <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6750,10 +6706,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6776,13 +6732,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>328</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>186</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6821,19 +6777,19 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC41" t="s" s="2">
+      <c r="AF41" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6845,7 +6801,7 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6859,10 +6815,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6885,16 +6841,16 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6902,7 +6858,7 @@
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>20</v>
@@ -6944,7 +6900,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -6959,7 +6915,7 @@
         <v>20</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6970,10 +6926,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6996,13 +6952,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7011,7 +6967,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>20</v>
@@ -7029,11 +6985,11 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7051,7 +7007,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -7063,10 +7019,10 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
@@ -7077,10 +7033,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7103,13 +7059,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7133,7 +7089,7 @@
         <v>20</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="X44" t="s" s="2">
         <v>20</v>
@@ -7160,7 +7116,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -7186,10 +7142,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7212,17 +7168,15 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7271,7 +7225,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -7280,27 +7234,27 @@
         <v>76</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK45" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7323,19 +7277,17 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7384,7 +7336,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -7393,27 +7345,27 @@
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AK46" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7436,19 +7388,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7485,17 +7437,17 @@
         <v>20</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -7504,30 +7456,30 @@
         <v>76</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AK47" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>20</v>
@@ -7549,19 +7501,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7610,7 +7562,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -7619,27 +7571,27 @@
         <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7662,13 +7614,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7719,7 +7671,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7734,7 +7686,7 @@
         <v>20</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -7745,14 +7697,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7771,16 +7723,16 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7818,19 +7770,19 @@
         <v>20</v>
       </c>
       <c r="AB50" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC50" t="s" s="2">
+      <c r="AF50" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7839,13 +7791,13 @@
         <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -7856,10 +7808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7882,17 +7834,15 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7902,7 +7852,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -7917,60 +7867,60 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7993,19 +7943,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8054,7 +8004,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -8063,27 +8013,27 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ52" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK52" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8106,19 +8056,19 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8143,13 +8093,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8167,7 +8117,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -8176,27 +8126,27 @@
         <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK53" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8219,16 +8169,16 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8278,7 +8228,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -8287,27 +8237,27 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK54" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8330,17 +8280,15 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8389,7 +8337,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -8398,30 +8346,30 @@
         <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AK55" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8443,19 +8391,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8504,7 +8452,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8513,27 +8461,27 @@
         <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AK56" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8556,13 +8504,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8613,7 +8561,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8628,7 +8576,7 @@
         <v>20</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>20</v>
@@ -8639,14 +8587,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8665,16 +8613,16 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8712,19 +8660,19 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC58" t="s" s="2">
+      <c r="AF58" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8733,13 +8681,13 @@
         <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>20</v>
@@ -8750,10 +8698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8776,17 +8724,15 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8796,7 +8742,7 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>20</v>
@@ -8811,60 +8757,60 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8887,19 +8833,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8948,7 +8894,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8957,27 +8903,27 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK60" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9000,19 +8946,19 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9037,13 +8983,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9061,7 +9007,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -9070,27 +9016,27 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK61" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9113,16 +9059,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9172,7 +9118,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -9181,27 +9127,27 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ62" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK62" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9224,17 +9170,15 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9283,7 +9227,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -9292,27 +9236,27 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ63" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AK63" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9335,19 +9279,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9372,13 +9316,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9396,7 +9340,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -9405,27 +9349,27 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ64" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK64" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9448,19 +9392,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9509,7 +9453,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -9518,27 +9462,27 @@
         <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK65" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9561,19 +9505,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9622,7 +9566,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9631,27 +9575,27 @@
         <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK66" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9674,13 +9618,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9731,7 +9675,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -9746,7 +9690,7 @@
         <v>20</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
@@ -9757,14 +9701,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9783,16 +9727,16 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9830,19 +9774,19 @@
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC68" t="s" s="2">
+      <c r="AF68" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9851,13 +9795,13 @@
         <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -9868,10 +9812,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9894,19 +9838,19 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -9919,7 +9863,7 @@
         <v>20</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>20</v>
@@ -9931,13 +9875,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9955,7 +9899,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9964,27 +9908,27 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK69" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10007,16 +9951,16 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10030,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>20</v>
@@ -10042,13 +9986,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10066,7 +10010,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -10075,27 +10019,27 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK70" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10118,19 +10062,19 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10143,7 +10087,7 @@
         <v>20</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>20</v>
@@ -10179,7 +10123,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -10188,27 +10132,27 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK71" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10231,17 +10175,15 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10254,7 +10196,7 @@
         <v>20</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>20</v>
@@ -10290,7 +10232,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -10299,31 +10241,31 @@
         <v>76</v>
       </c>
       <c r="AI72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ72" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK72" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10342,17 +10284,15 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10365,7 +10305,7 @@
         <v>20</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>20</v>
@@ -10401,7 +10341,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10410,31 +10350,31 @@
         <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ73" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK73" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10453,16 +10393,16 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10476,7 +10416,7 @@
         <v>20</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>20</v>
@@ -10512,7 +10452,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10521,31 +10461,31 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ74" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK74" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10564,17 +10504,15 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -10623,7 +10561,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10632,31 +10570,31 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ75" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK75" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10675,17 +10613,15 @@
         <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -10698,7 +10634,7 @@
         <v>20</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>20</v>
@@ -10734,7 +10670,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10743,27 +10679,27 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK76" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10786,16 +10722,16 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10845,7 +10781,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10854,27 +10790,27 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK77" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10897,19 +10833,17 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -10922,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>20</v>
@@ -10958,7 +10892,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10967,27 +10901,27 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AK78" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11010,17 +10944,15 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11069,36 +11001,36 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>541</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11121,19 +11053,17 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11182,7 +11112,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -11191,13 +11121,13 @@
         <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ80" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="AK80" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -11208,10 +11138,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11234,13 +11164,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11291,7 +11221,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -11306,7 +11236,7 @@
         <v>20</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>20</v>
@@ -11317,14 +11247,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11343,16 +11273,16 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11390,19 +11320,19 @@
         <v>20</v>
       </c>
       <c r="AB82" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE82" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC82" t="s" s="2">
+      <c r="AF82" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -11411,13 +11341,13 @@
         <v>76</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>20</v>
@@ -11428,10 +11358,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11454,16 +11384,16 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11513,7 +11443,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
@@ -11522,13 +11452,13 @@
         <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>20</v>
@@ -11539,10 +11469,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11565,16 +11495,16 @@
         <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11600,13 +11530,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -11624,7 +11554,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11633,13 +11563,13 @@
         <v>84</v>
       </c>
       <c r="AI84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ84" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK84" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>20</v>
@@ -11650,10 +11580,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11676,16 +11606,16 @@
         <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11735,7 +11665,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11744,27 +11674,27 @@
         <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ85" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK85" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11787,13 +11717,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11844,7 +11774,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -11859,7 +11789,7 @@
         <v>20</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>20</v>
@@ -11870,14 +11800,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11896,16 +11826,16 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11943,19 +11873,19 @@
         <v>20</v>
       </c>
       <c r="AB87" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE87" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC87" t="s" s="2">
+      <c r="AF87" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11964,13 +11894,13 @@
         <v>76</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>20</v>
@@ -11981,10 +11911,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12007,19 +11937,19 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12044,60 +11974,60 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Y88" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="Y88" t="s" s="2">
+      <c r="Z88" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="Z88" t="s" s="2">
+      <c r="AA88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AA88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF88" t="s" s="2">
+      <c r="AG88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK88" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AG88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>218</v>
-      </c>
       <c r="AL88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12120,19 +12050,19 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12157,60 +12087,60 @@
         <v>20</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AA89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF89" t="s" s="2">
+      <c r="AG89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12233,19 +12163,19 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12258,72 +12188,72 @@
         <v>20</v>
       </c>
       <c r="T90" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="U90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF90" t="s" s="2">
+      <c r="AG90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK90" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AG90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK90" t="s" s="2">
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12346,16 +12276,16 @@
         <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12369,72 +12299,72 @@
         <v>20</v>
       </c>
       <c r="T91" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="U91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AG91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK91" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AG91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK91" t="s" s="2">
+      <c r="AL91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12457,17 +12387,15 @@
         <v>85</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -12516,36 +12444,36 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>254</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12568,16 +12496,16 @@
         <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12627,7 +12555,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12636,27 +12564,27 @@
         <v>84</v>
       </c>
       <c r="AI93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ93" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="AK93" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12679,16 +12607,16 @@
         <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12738,7 +12666,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12747,13 +12675,13 @@
         <v>84</v>
       </c>
       <c r="AI94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ94" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK94" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>20</v>
@@ -12764,10 +12692,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12790,17 +12718,17 @@
         <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -12849,7 +12777,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12858,16 +12786,16 @@
         <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ95" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK95" t="s" s="2">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>20</v>
@@ -12875,10 +12803,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12901,13 +12829,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12958,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12967,13 +12895,13 @@
         <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ96" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK96" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>
@@ -12984,10 +12912,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13010,13 +12938,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13067,7 +12995,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -13082,7 +13010,7 @@
         <v>20</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>20</v>
@@ -13093,14 +13021,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13119,16 +13047,16 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13166,19 +13094,19 @@
         <v>20</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="AC98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -13187,13 +13115,13 @@
         <v>76</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>20</v>
@@ -13204,14 +13132,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13230,19 +13158,19 @@
         <v>85</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -13291,7 +13219,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -13300,13 +13228,13 @@
         <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>20</v>
@@ -13317,10 +13245,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13343,17 +13271,15 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -13402,7 +13328,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>84</v>
@@ -13411,13 +13337,13 @@
         <v>84</v>
       </c>
       <c r="AI100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ100" t="s" s="2">
-        <v>261</v>
-      </c>
       <c r="AK100" t="s" s="2">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>20</v>
@@ -13428,10 +13354,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13454,13 +13380,13 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13511,7 +13437,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -13526,7 +13452,7 @@
         <v>20</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>20</v>
@@ -13537,14 +13463,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13563,16 +13489,16 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13610,19 +13536,19 @@
         <v>20</v>
       </c>
       <c r="AB102" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE102" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="AC102" t="s" s="2">
+      <c r="AF102" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13631,13 +13557,13 @@
         <v>76</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>20</v>
@@ -13648,10 +13574,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13674,16 +13600,16 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13733,7 +13659,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -13742,13 +13668,13 @@
         <v>84</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>20</v>
@@ -13759,10 +13685,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13785,16 +13711,16 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13820,13 +13746,13 @@
         <v>20</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>20</v>
@@ -13844,7 +13770,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13853,13 +13779,13 @@
         <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ104" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK104" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>20</v>
@@ -13870,10 +13796,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13896,16 +13822,16 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13955,7 +13881,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -13964,27 +13890,27 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ105" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK105" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>569</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14007,16 +13933,16 @@
         <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14066,7 +13992,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -14075,13 +14001,13 @@
         <v>84</v>
       </c>
       <c r="AI106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ106" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK106" t="s" s="2">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>20</v>
@@ -14092,10 +14018,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14118,17 +14044,15 @@
         <v>20</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -14153,13 +14077,13 @@
         <v>20</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14177,7 +14101,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -14186,13 +14110,13 @@
         <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AJ107" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK107" t="s" s="2">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>20</v>
